--- a/export/season_plan_spond.xlsx
+++ b/export/season_plan_spond.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E330"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Ringerike 1</t>
+          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
+          <t>U10: Jutul 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 1</t>
+          <t>U10: Tønsberg 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Frisk Asker 1</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Holmen 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Skien 1</t>
+          <t>U10: Jar 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 1</t>
+          <t>U10: Ringerike 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Skien 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Ringerike 1</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Jutul 1</t>
+          <t>U10: Jar 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 1</t>
+          <t>U10: Kongsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jar 1</t>
+          <t>U10: Holmen 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Jutul 1</t>
+          <t>U10: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Frisk Asker 1</t>
+          <t>U10: Jar 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Ringerike 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -994,17 +994,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Jutul 1</t>
+          <t>U10: Sandefjord 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1013,17 +1013,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1032,17 +1032,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1051,17 +1051,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jar 2</t>
+          <t>U10: Kongsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1070,17 +1070,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Jar 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1089,17 +1089,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1108,17 +1108,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Tønsberg 1</t>
+          <t>U10: Holmen 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1127,17 +1127,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Ringerike 2</t>
+          <t>U10: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Frisk Asker 2</t>
+          <t>U11: Jar 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 2</t>
+          <t>U11: Frisk Asker 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Tønsberg 1</t>
+          <t>U11: Ringerike 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Sandefjord 1</t>
+          <t>U11: Jutul 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Frisk Asker 2</t>
+          <t>U11: Sandefjord 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jutul 1</t>
+          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Jar 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1279,17 +1279,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Sandefjord 1</t>
+          <t>U11: Jutul 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1298,17 +1298,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
+          <t>U11: Holmen 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1317,17 +1317,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U11: Ringerike 2 vs Jar 2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1336,17 +1336,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Skien 1</t>
+          <t>U11: Frisk Asker 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1355,17 +1355,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 3</t>
+          <t>U11: Holmen 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1374,17 +1374,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Jar 2 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1393,17 +1393,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 3</t>
+          <t>U11: Ringerike 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1412,17 +1412,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Holmen 1</t>
+          <t>U11: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Holmen 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Skien 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Ringerike 2</t>
+          <t>U10: Ringerike 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Holmen 1</t>
+          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 3</t>
+          <t>U10: Holmen 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Sandefjord 1</t>
+          <t>U10: Kongsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Ringerike 2</t>
+          <t>U10: Jar 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 3</t>
+          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 3</t>
+          <t>U10: Sandefjord 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Ringerike 2</t>
+          <t>U10: Tønsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
+          <t>U10: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Frisk Asker 3</t>
+          <t>U10: Jar 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Kongsberg 1</t>
+          <t>U10: Jutul 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U10: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Holmen 1</t>
+          <t>U10: Kongsberg 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1830,17 +1830,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Jutul 1</t>
+          <t>U10: Ringerike 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1849,17 +1849,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1868,17 +1868,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Jar 4</t>
+          <t>U10: Frisk Asker 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1887,17 +1887,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Holmen 1</t>
+          <t>U10: Jar 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1906,17 +1906,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1925,17 +1925,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Tønsberg 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -1944,17 +1944,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Ringerike 2</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1963,17 +1963,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Frisk Asker 1</t>
+          <t>U10: Skien 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 4</t>
+          <t>U10: Frisk Asker 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2001,17 +2001,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Tønsberg 1</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2020,17 +2020,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Jutul 1</t>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2039,17 +2039,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Frisk Asker 1</t>
+          <t>U10: Jar 3 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2058,17 +2058,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Holmen 1</t>
+          <t>U10: Ringerike 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2077,17 +2077,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2096,17 +2096,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2115,17 +2115,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Jutul 1</t>
+          <t>U11: Jar 4 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2134,17 +2134,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Kongsberg 1</t>
+          <t>U11: Frisk Asker 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2153,17 +2153,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U11: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2172,17 +2172,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Jar 5</t>
+          <t>U11: Kongsberg 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2191,17 +2191,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U11: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2210,17 +2210,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
+          <t>U11: Ringerike 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2229,17 +2229,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 1</t>
+          <t>U11: Jar 4 vs Skien 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2248,17 +2248,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Kongsberg 1</t>
+          <t>U11: Kongsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2267,17 +2267,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
+          <t>U11: Tønsberg 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2286,17 +2286,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U11: Ringerike 2 vs Jar 4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2305,17 +2305,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Ringerike 1</t>
+          <t>U11: Frisk Asker 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2324,17 +2324,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 5</t>
+          <t>U11: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2343,17 +2343,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U11: Jar 4 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2362,17 +2362,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jutul 1</t>
+          <t>U11: Ringerike 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2381,17 +2381,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Holmen 1</t>
+          <t>U11: Skien 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Skien 1</t>
+          <t>U10: Frisk Asker 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Ringerike 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Frisk Asker 2</t>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 5</t>
+          <t>U10: Holmen 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Kongsberg 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Frisk Asker 2</t>
+          <t>U10: Jar 5 vs Jutul 1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Ringerike 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2628,17 +2628,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2647,17 +2647,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2666,17 +2666,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -2685,17 +2685,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jar 6</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -2704,17 +2704,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Skien 1</t>
+          <t>U10: Jar 5 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -2723,17 +2723,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Frisk Asker 3</t>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -2742,17 +2742,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Jutul 1</t>
+          <t>U10: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -2761,17 +2761,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Ringerike 1</t>
+          <t>U10: Holmen 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -2780,17 +2780,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Frisk Asker 3</t>
+          <t>U10: Kongsberg 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -2799,17 +2799,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jar 6</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2818,17 +2818,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -2837,17 +2837,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -2856,17 +2856,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Frisk Asker 3</t>
+          <t>U10: Jar 5 vs Skien 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -2875,17 +2875,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Skien 1</t>
+          <t>U10: Kongsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -2894,17 +2894,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -2913,17 +2913,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Skien 1</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -2932,17 +2932,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Holmen 1</t>
+          <t>U10: Ringerike 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -2951,17 +2951,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -2970,17 +2970,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -2989,17 +2989,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 7</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3008,17 +3008,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
+          <t>U10: Jar 5 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3027,17 +3027,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Frisk Asker 1</t>
+          <t>U10: Skien 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3046,17 +3046,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Kongsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3065,17 +3065,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3084,17 +3084,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U11: Jar 6 vs Jutul 1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3103,17 +3103,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U11: Frisk Asker 3 vs Skien 1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3122,17 +3122,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Ringerike 1</t>
+          <t>U11: Ringerike 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3141,17 +3141,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 7</t>
+          <t>U11: Skien 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3160,17 +3160,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3179,17 +3179,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U11: Ringerike 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Skien 1</t>
+          <t>U11: Jar 6 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3217,17 +3217,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Tønsberg 1</t>
+          <t>U11: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3236,17 +3236,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U11: Jutul 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3255,17 +3255,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
+          <t>U11: Ringerike 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3274,17 +3274,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -3293,17 +3293,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 7</t>
+          <t>U11: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
+          <t>U11: Jar 6 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3331,17 +3331,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U11: Ringerike 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3350,17 +3350,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U11: Sandefjord 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Frisk Asker 1</t>
+          <t>U10: Frisk Asker 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U10: Ringerike 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3445,17 +3445,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -3464,17 +3464,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -3483,17 +3483,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -3502,17 +3502,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jar 1</t>
+          <t>U10: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -3521,17 +3521,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Jar 7 vs Jutul 1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -3540,17 +3540,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -3559,17 +3559,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -3578,17 +3578,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Ringerike 2</t>
+          <t>U10: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -3597,17 +3597,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Frisk Asker 2</t>
+          <t>U10: Sandefjord 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -3616,17 +3616,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 1</t>
+          <t>U10: Tønsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -3635,17 +3635,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Kongsberg 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -3654,17 +3654,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -3673,17 +3673,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Frisk Asker 2</t>
+          <t>U10: Jar 7 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -3692,17 +3692,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jutul 1</t>
+          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -3711,17 +3711,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -3730,17 +3730,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Skien 1</t>
+          <t>U10: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -3749,17 +3749,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -3768,17 +3768,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Tønsberg 1</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -3787,17 +3787,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Ringerike 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -3806,17 +3806,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Jar 2</t>
+          <t>U10: Frisk Asker 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -3825,17 +3825,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U10: Jar 7 vs Holmen 1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -3844,17 +3844,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Frisk Asker 3</t>
+          <t>U10: Kongsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -3863,17 +3863,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Ringerike 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -3882,17 +3882,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Tønsberg 1</t>
+          <t>U10: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -3901,17 +3901,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Kongsberg 1</t>
+          <t>U10: Ringerike 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -3920,17 +3920,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U10: Frisk Asker 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -3939,17 +3939,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Ringerike 1</t>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -3958,17 +3958,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 2</t>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -3977,17 +3977,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Jar 7 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -3996,17 +3996,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4015,17 +4015,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Skien 1</t>
+          <t>U10: Kongsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4034,17 +4034,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4053,17 +4053,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U11: Jar 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4072,17 +4072,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 3</t>
+          <t>U11: Frisk Asker 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -4091,17 +4091,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U11: Ringerike 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -4110,17 +4110,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 2</t>
+          <t>U11: Holmen 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4129,17 +4129,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Holmen 1</t>
+          <t>U11: Kongsberg 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4148,17 +4148,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -4167,17 +4167,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
+          <t>U11: Jar 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -4186,17 +4186,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Frisk Asker 3</t>
+          <t>U11: Holmen 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -4205,17 +4205,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U11: Tønsberg 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -4224,17 +4224,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jutul 1</t>
+          <t>U11: Ringerike 2 vs Jar 1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -4243,17 +4243,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U11: Frisk Asker 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -4262,17 +4262,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Tønsberg 1</t>
+          <t>U11: Tønsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -4281,17 +4281,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Sandefjord 1</t>
+          <t>U11: Jar 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -4300,17 +4300,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jutul 1</t>
+          <t>U11: Ringerike 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -4319,17 +4319,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jar 3</t>
+          <t>U11: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -4338,17 +4338,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -4357,17 +4357,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Frisk Asker 1</t>
+          <t>U10: Ringerike 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -4376,17 +4376,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -4395,17 +4395,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Ringerike 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -4414,17 +4414,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Frisk Asker 1</t>
+          <t>U10: Jutul 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -4433,17 +4433,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jar 3</t>
+          <t>U10: Holmen 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -4452,17 +4452,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Jutul 1</t>
+          <t>U10: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -4471,17 +4471,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -4490,17 +4490,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Frisk Asker 1</t>
+          <t>U10: Jar 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -4509,17 +4509,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Tønsberg 1</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -4528,17 +4528,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -4547,17 +4547,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Tønsberg 1</t>
+          <t>U10: Ringerike 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -4566,17 +4566,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -4585,17 +4585,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -4604,17 +4604,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -4623,17 +4623,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 4</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -4642,17 +4642,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
+          <t>U10: Jar 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -4661,17 +4661,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Frisk Asker 2</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -4680,17 +4680,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Skien 1</t>
+          <t>U10: Skien 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -4699,17 +4699,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Sandefjord 1</t>
+          <t>U10: Jutul 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -4718,17 +4718,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -4737,17 +4737,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 2</t>
+          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -4756,17 +4756,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Skien 1</t>
+          <t>U10: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -4775,17 +4775,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 4</t>
+          <t>U10: Frisk Asker 3 vs Skien 1</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -4794,17 +4794,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Sandefjord 1</t>
+          <t>U10: Jar 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -4813,17 +4813,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -4832,17 +4832,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -4851,17 +4851,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Ringerike 2</t>
+          <t>U10: Skien 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -4870,17 +4870,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Ringerike 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -4889,17 +4889,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
+          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -4908,17 +4908,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -4927,17 +4927,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 4</t>
+          <t>U10: Skien 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -4946,17 +4946,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Ringerike 2</t>
+          <t>U10: Jar 2 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -4965,17 +4965,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Kongsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -4984,17 +4984,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -5003,17 +5003,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Frisk Asker 2</t>
+          <t>U10: Sandefjord 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -5022,12 +5022,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U11: Jar 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5041,12 +5041,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Holmen 1</t>
+          <t>U11: Frisk Asker 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5060,12 +5060,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U11: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5079,12 +5079,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Jutul 1</t>
+          <t>U11: Sandefjord 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5098,12 +5098,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Holmen 1</t>
+          <t>U11: Holmen 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Sandefjord 1</t>
+          <t>U11: Ringerike 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5136,12 +5136,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Jar 5</t>
+          <t>U11: Jar 3 vs Holmen 1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5155,12 +5155,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jutul 1</t>
+          <t>U11: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 3</t>
+          <t>U11: Kongsberg 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5193,12 +5193,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Sandefjord 1</t>
+          <t>U11: Ringerike 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5212,12 +5212,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Ringerike 2</t>
+          <t>U11: Frisk Asker 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Frisk Asker 3</t>
+          <t>U11: Kongsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5250,12 +5250,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 5</t>
+          <t>U11: Jar 3 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5269,12 +5269,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
+          <t>U11: Ringerike 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5288,12 +5288,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Holmen 1</t>
+          <t>U11: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5307,12 +5307,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Frisk Asker 3</t>
+          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -5326,12 +5326,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5345,12 +5345,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5364,12 +5364,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5383,12 +5383,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
+          <t>U10: Kongsberg 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Jutul 1</t>
+          <t>U10: Holmen 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5421,12 +5421,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5440,12 +5440,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 6</t>
+          <t>U10: Tønsberg 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5459,12 +5459,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U10: Jar 4 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 1</t>
+          <t>U10: Kongsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 2</t>
+          <t>U10: Frisk Asker 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5516,12 +5516,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5535,12 +5535,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U10: Holmen 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5554,12 +5554,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5573,12 +5573,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Ringerike 2</t>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5592,12 +5592,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 6</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5611,12 +5611,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Jar 4 vs Skien 1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5630,12 +5630,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5649,12 +5649,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Holmen 1</t>
+          <t>U10: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5668,12 +5668,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Kongsberg 1</t>
+          <t>U10: Kongsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5687,12 +5687,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 2</t>
+          <t>U10: Tønsberg 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Frisk Asker 1</t>
+          <t>U10: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5725,12 +5725,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Holmen 1</t>
+          <t>U10: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5744,12 +5744,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Jar 6</t>
+          <t>U10: Frisk Asker 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
+          <t>U10: Jar 4 vs Jutul 1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5782,12 +5782,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -5801,12 +5801,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5820,12 +5820,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Frisk Asker 1</t>
+          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -5839,12 +5839,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Holmen 1</t>
+          <t>U10: Ringerike 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5877,12 +5877,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -5896,17 +5896,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -5915,17 +5915,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Kongsberg 1</t>
+          <t>U10: Jar 4 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -5934,17 +5934,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Jutul 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -5953,17 +5953,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Jar 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -5972,17 +5972,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -5991,17 +5991,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Frisk Asker 3</t>
+          <t>U11: Jar 5 vs Skien 1</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -6010,17 +6010,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Ringerike 1</t>
+          <t>U11: Frisk Asker 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -6029,17 +6029,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U11: Ringerike 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -6048,17 +6048,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Frisk Asker 3</t>
+          <t>U11: Tønsberg 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -6067,17 +6067,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Jar 1</t>
+          <t>U11: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -6086,17 +6086,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Ringerike 1</t>
+          <t>U11: Ringerike 2 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -6105,17 +6105,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U11: Jar 5 vs Jutul 1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -6124,17 +6124,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Frisk Asker 3</t>
+          <t>U11: Tønsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -6143,17 +6143,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Skien 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -6162,17 +6162,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Kongsberg 1</t>
+          <t>U11: Ringerike 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -6181,17 +6181,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Kongsberg 1</t>
+          <t>U11: Frisk Asker 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -6200,17 +6200,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Sandefjord 1</t>
+          <t>U11: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -6219,17 +6219,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U11: Jar 5 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -6238,17 +6238,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jutul 1</t>
+          <t>U11: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -6257,17 +6257,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jar 7</t>
+          <t>U11: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -6276,17 +6276,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -6295,17 +6295,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Frisk Asker 2</t>
+          <t>U10: Ringerike 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -6314,17 +6314,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Ringerike 1</t>
+          <t>U10: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -6333,17 +6333,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Skien 1</t>
+          <t>U10: Jutul 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -6352,17 +6352,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Tønsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -6371,17 +6371,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -6390,17 +6390,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Ringerike 1</t>
+          <t>U10: Kongsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -6409,17 +6409,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Jar 7</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -6428,17 +6428,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Jar 6 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -6447,17 +6447,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Sandefjord 1</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -6466,17 +6466,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -6485,17 +6485,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Holmen 1</t>
+          <t>U10: Ringerike 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -6504,17 +6504,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Ringerike 1</t>
+          <t>U10: Skien 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -6523,17 +6523,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 2</t>
+          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -6542,17 +6542,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -6561,17 +6561,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 7</t>
+          <t>U10: Ringerike 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -6580,17 +6580,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Holmen 1</t>
+          <t>U10: Jar 6 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -6599,17 +6599,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -6618,17 +6618,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
+          <t>U10: Sandefjord 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -6637,17 +6637,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Frisk Asker 2</t>
+          <t>U10: Tønsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -6656,17 +6656,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Kongsberg 1</t>
+          <t>U10: Jutul 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -6675,17 +6675,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Holmen 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -6694,21 +6694,1237 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>18.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>U10: Jar 6 vs Holmen 1</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>U10: Jutul 1 vs Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Jar 6</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 1 vs Holmen 1</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>U10: Jar 6 vs Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>U11: Jar 1 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>U11: Frisk Asker 3 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>U11: Ringerike 2 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>U11: Kongsberg 1 vs Jar 1</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>U11: Sandefjord 1 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>U11: Ringerike 2 vs Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>U11: Jar 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>U11: Kongsberg 1 vs Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>U11: Jutul 1 vs Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>U11: Ringerike 2 vs Jar 1</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>U11: Jutul 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>U11: Jar 1 vs Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>U11: Ringerike 2 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>U11: Sandefjord 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Jar 7</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>U10: Jar 7 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 2 vs Holmen 1</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>U10: Tønsberg 1 vs Jar 7</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>U10: Jar 7 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>U10: Tønsberg 1 vs Holmen 1</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>U10: Jutul 1 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Jar 7</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 2 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>U10: Jar 7 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>U10: Jutul 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>U10: Ringerike 2 vs Jar 7</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>U10: Frisk Asker 2 vs Skien 1</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>U10: Jar 7 vs Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>U10: Skien 1 vs Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>U10: Holmen 1 vs Jutul 1</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/export/season_plan_spond.xlsx
+++ b/export/season_plan_spond.xlsx
@@ -427,7 +427,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
   </cols>
@@ -472,7 +472,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -529,7 +529,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>

--- a/export/season_plan_spond.xlsx
+++ b/export/season_plan_spond.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
+          <t>U10: Jar 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U10: Jar 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Ringerike 1</t>
+          <t>U10: Jar 4 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Holmen 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 1</t>
+          <t>U10: Sandefjord 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Frisk Asker 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jutul 1</t>
+          <t>U10: Jar 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Kongsberg 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Jar 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Holmen 1</t>
+          <t>U10: Sandefjord 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 1</t>
+          <t>U10: Frisk Asker 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U10: Jar 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
+          <t>U10: Jutul 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Skien 1</t>
+          <t>U10: Holmen 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Jar 4 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U10: Jar 3 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 1</t>
+          <t>U10: Jar 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Ringerike 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Jutul 1</t>
+          <t>U10: Holmen 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 1</t>
+          <t>U10: Jar 4 vs Holmen 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jar 1</t>
+          <t>U10: Frisk Asker 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1013,12 +1013,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Jutul 1</t>
+          <t>U11: Jar 5 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1032,12 +1032,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U11: Jar 6 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U11: Frisk Asker 3 vs Skien 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U10: Jar 1 vs Frisk Asker 1</t>
+          <t>U11: Ringerike 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1089,12 +1089,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
+          <t>U11: Skien 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U11: Frisk Asker 3 vs Jar 6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 1</t>
+          <t>U11: Jar 5 vs Skien 1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Holmen 1</t>
+          <t>U11: Ringerike 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Jutul 1</t>
+          <t>U11: Kongsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Sandefjord 1</t>
+          <t>U11: Frisk Asker 3 vs Jar 5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Jar 2</t>
+          <t>U11: Jar 6 vs Skien 1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Holmen 1</t>
+          <t>U11: Kongsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
+          <t>U11: Frisk Asker 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Sandefjord 1</t>
+          <t>U11: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1279,17 +1279,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Ringerike 2</t>
+          <t>U10: Ringerike 2 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1298,17 +1298,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Frisk Asker 2</t>
+          <t>U10: Tønsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1317,17 +1317,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 2</t>
+          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1336,17 +1336,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1355,17 +1355,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1374,17 +1374,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U11: Jar 2 vs Frisk Asker 2</t>
+          <t>U10: Kongsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1393,17 +1393,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1412,17 +1412,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Holmen 1</t>
+          <t>U10: Jar 7 vs Holmen 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Sandefjord 1</t>
+          <t>U10: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 3</t>
+          <t>U10: Kongsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 3</t>
+          <t>U10: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 2</t>
+          <t>U10: Tønsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Jutul 1</t>
+          <t>U10: Jar 7 vs Jutul 1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
+          <t>U10: Holmen 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 2</t>
+          <t>U10: Frisk Asker 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jar 3</t>
+          <t>U10: Skien 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Sandefjord 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 3</t>
+          <t>U10: Ringerike 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Tønsberg 1</t>
+          <t>U10: Jar 7 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Holmen 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 3</t>
+          <t>U10: Tønsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Ringerike 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Jutul 1</t>
+          <t>U10: Holmen 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Ringerike 2</t>
+          <t>U10: Jar 7 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 3</t>
+          <t>U10: Skien 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1963,17 +1963,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 3</t>
+          <t>U11: Tønsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Ringerike 2</t>
+          <t>U11: Ringerike 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2001,17 +2001,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U11: Jar 5 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2020,17 +2020,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Sandefjord 1</t>
+          <t>U11: Frisk Asker 2 vs Jar 6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2039,17 +2039,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U10: Jar 3 vs Frisk Asker 3</t>
+          <t>U11: Frisk Asker 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2058,17 +2058,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Holmen 1</t>
+          <t>U11: Tønsberg 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2077,17 +2077,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U11: Jar 5 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2096,17 +2096,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Jar 6 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Tønsberg 1</t>
+          <t>U11: Frisk Asker 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Kongsberg 1</t>
+          <t>U11: Ringerike 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Skien 1</t>
+          <t>U11: Tønsberg 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Jar 4</t>
+          <t>U11: Frisk Asker 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Tønsberg 1</t>
+          <t>U11: Frisk Asker 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2210,17 +2210,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 1</t>
+          <t>U10: Ringerike 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2229,17 +2229,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Skien 1</t>
+          <t>U10: Jar 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2248,17 +2248,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Ringerike 2</t>
+          <t>U10: Jar 7 vs Skien 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2267,17 +2267,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Frisk Asker 1</t>
+          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2286,17 +2286,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 4</t>
+          <t>U10: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2305,17 +2305,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Skien 1</t>
+          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2324,17 +2324,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Kongsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2343,17 +2343,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U11: Jar 4 vs Frisk Asker 1</t>
+          <t>U10: Ringerike 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2362,17 +2362,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Skien 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2381,17 +2381,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Kongsberg 1</t>
+          <t>U10: Jar 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sandefjord ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Holmen 1</t>
+          <t>U10: Jar 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Jar 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 5</t>
+          <t>U10: Tønsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
+          <t>U10: Kongsberg 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Ringerike 1</t>
+          <t>U10: Jar 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Jar 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Sandefjord 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
+          <t>U10: Jar 3 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 5</t>
+          <t>U10: Jar 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Kongsberg 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Frisk Asker 2</t>
+          <t>U10: Tønsberg 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Jar 7 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Jar 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Ringerike 1</t>
+          <t>U10: Jar 3 vs Skien 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 5</t>
+          <t>U11: Jutul 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U11: Ringerike 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2818,12 +2818,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Tønsberg 1</t>
+          <t>U11: Jar 6 vs Jutul 1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2837,12 +2837,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Jutul 1</t>
+          <t>U11: Jar 5 vs Holmen 1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2856,12 +2856,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Skien 1</t>
+          <t>U11: Jar 4 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2875,12 +2875,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U11: Jutul 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2894,12 +2894,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
+          <t>U11: Holmen 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U11: Jar 4 vs Jutul 1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2932,12 +2932,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 5</t>
+          <t>U11: Ringerike 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2951,12 +2951,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Skien 1</t>
+          <t>U11: Holmen 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2970,12 +2970,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U11: Jutul 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2989,12 +2989,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
+          <t>U11: Jar 4 vs Holmen 1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3008,17 +3008,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>U10: Jar 5 vs Frisk Asker 2</t>
+          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3027,17 +3027,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3046,17 +3046,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3065,17 +3065,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
+          <t>U10: Kongsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3084,17 +3084,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Jutul 1</t>
+          <t>U10: Jar 5 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3103,17 +3103,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Skien 1</t>
+          <t>U10: Jar 7 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3122,17 +3122,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Sandefjord 1</t>
+          <t>U10: Jar 4 vs Skien 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3141,17 +3141,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Jar 6</t>
+          <t>U10: Ringerike 2 vs Jar 1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3160,17 +3160,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Kongsberg 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3179,17 +3179,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Frisk Asker 3</t>
+          <t>U10: Frisk Asker 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3217,17 +3217,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Ringerike 1</t>
+          <t>U10: Jar 5 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3236,17 +3236,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Frisk Asker 3</t>
+          <t>U10: Jar 4 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3255,17 +3255,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jar 6</t>
+          <t>U10: Ringerike 2 vs Jar 7</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3274,17 +3274,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
+          <t>U10: Jar 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -3293,17 +3293,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Skien 1</t>
+          <t>U10: Kongsberg 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>U11: Jar 6 vs Frisk Asker 3</t>
+          <t>U10: Jar 4 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3331,17 +3331,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3350,17 +3350,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Skien 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Skien 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
+          <t>U10: Jar 4 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Jar 7 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 7</t>
+          <t>U10: Jar 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 1</t>
+          <t>U10: Frisk Asker 2 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Frisk Asker 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Kongsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Jutul 1</t>
+          <t>U10: Ringerike 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3559,17 +3559,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Kongsberg 1</t>
+          <t>U11: Sandefjord 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -3578,17 +3578,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U11: Jar 6 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -3597,17 +3597,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jar 7</t>
+          <t>U11: Ringerike 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -3616,17 +3616,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jutul 1</t>
+          <t>U11: Jar 4 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -3635,17 +3635,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U11: Sandefjord 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -3654,17 +3654,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Frisk Asker 1</t>
+          <t>U11: Ringerike 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -3673,17 +3673,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Tønsberg 1</t>
+          <t>U11: Frisk Asker 3 vs Jar 6</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -3692,17 +3692,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U11: Jar 5 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -3711,17 +3711,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U11: Frisk Asker 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -3730,17 +3730,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 1</t>
+          <t>U11: Sandefjord 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -3749,17 +3749,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 7</t>
+          <t>U11: Jar 5 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -3768,17 +3768,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U11: Jar 4 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -3787,17 +3787,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Sandefjord 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -3806,17 +3806,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Jutul 1</t>
+          <t>U10: Jar 4 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -3825,17 +3825,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Holmen 1</t>
+          <t>U10: Jar 2 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -3844,17 +3844,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U10: Frisk Asker 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -3863,17 +3863,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 1</t>
+          <t>U10: Ringerike 2 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -3882,17 +3882,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Jutul 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -3901,17 +3901,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 7</t>
+          <t>U10: Frisk Asker 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -3920,17 +3920,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -3939,17 +3939,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
+          <t>U10: Ringerike 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -3958,17 +3958,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Jar 3 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -3977,17 +3977,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>U10: Jar 7 vs Frisk Asker 1</t>
+          <t>U10: Jar 6 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -3996,17 +3996,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Jar 4 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4015,17 +4015,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Jutul 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4034,17 +4034,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U10: Ringerike 2 vs Jar 6</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4053,12 +4053,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 2</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4072,12 +4072,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Holmen 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4091,12 +4091,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Kongsberg 1</t>
+          <t>U10: Jar 6 vs Jutul 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4110,12 +4110,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Jar 1</t>
+          <t>U10: Jar 4 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4129,12 +4129,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Tønsberg 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4148,12 +4148,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 2</t>
+          <t>U10: Jutul 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Kongsberg 1</t>
+          <t>U10: Jar 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4186,12 +4186,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Ringerike 2</t>
+          <t>U10: Jar 4 vs Jutul 1</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4205,12 +4205,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Frisk Asker 2</t>
+          <t>U10: Tønsberg 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4224,12 +4224,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4243,12 +4243,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 2 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4262,12 +4262,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4281,12 +4281,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>U11: Jar 1 vs Frisk Asker 2</t>
+          <t>U10: Jar 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4300,12 +4300,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Tønsberg 1</t>
+          <t>U10: Jar 6 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4319,12 +4319,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Jar 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4338,17 +4338,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Jutul 1</t>
+          <t>U11: Holmen 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -4357,17 +4357,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Skien 1</t>
+          <t>U11: Skien 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -4376,17 +4376,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U11: Ringerike 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -4395,17 +4395,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Frisk Asker 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -4414,17 +4414,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Jar 2</t>
+          <t>U11: Frisk Asker 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -4433,17 +4433,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Frisk Asker 3</t>
+          <t>U11: Holmen 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -4452,17 +4452,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Ringerike 1</t>
+          <t>U11: Ringerike 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -4471,17 +4471,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U11: Jar 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -4490,17 +4490,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Skien 1</t>
+          <t>U11: Frisk Asker 2 vs Holmen 1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -4509,17 +4509,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U11: Skien 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -4528,17 +4528,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Tønsberg 1</t>
+          <t>U11: Jar 2 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -4547,17 +4547,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Kongsberg 1</t>
+          <t>U11: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -4566,17 +4566,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 2</t>
+          <t>U11: Frisk Asker 2 vs Jar 2</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -4585,17 +4585,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
+          <t>U11: Frisk Asker 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -4604,17 +4604,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Ringerike 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -4623,17 +4623,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Frisk Asker 3</t>
+          <t>U10: Jutul 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -4642,17 +4642,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 7</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -4661,17 +4661,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -4680,17 +4680,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
+          <t>U10: Jar 5 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -4699,17 +4699,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Ringerike 1</t>
+          <t>U10: Jar 7 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -4718,17 +4718,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 2</t>
+          <t>U10: Jar 1 vs Jutul 1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -4737,17 +4737,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Sandefjord 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -4756,17 +4756,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -4775,17 +4775,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Skien 1</t>
+          <t>U10: Jutul 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -4794,17 +4794,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Kongsberg 1</t>
+          <t>U10: Jar 7 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -4813,17 +4813,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 5</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -4832,17 +4832,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 3</t>
+          <t>U10: Jutul 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -4851,17 +4851,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jutul 1</t>
+          <t>U10: Sandefjord 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -4870,17 +4870,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 2</t>
+          <t>U10: Jar 7 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -4889,17 +4889,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 3 vs Kongsberg 1</t>
+          <t>U10: Jar 3 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -4908,17 +4908,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Sandefjord 1</t>
+          <t>U10: Jar 5 vs Jutul 1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -4927,17 +4927,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U10: Frisk Asker 3 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -4946,17 +4946,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>U10: Jar 2 vs Frisk Asker 3</t>
+          <t>U10: Frisk Asker 2 vs Jar 1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -4965,17 +4965,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jutul 1</t>
+          <t>U10: Jutul 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -4984,17 +4984,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U10: Ringerike 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -5003,17 +5003,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Holmen 1</t>
+          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -5022,12 +5022,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Kongsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5041,12 +5041,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Sandefjord 1</t>
+          <t>U10: Jar 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5060,12 +5060,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5079,12 +5079,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Jar 3</t>
+          <t>U10: Ringerike 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5098,12 +5098,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Sandefjord 1 vs Ringerike 1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Frisk Asker 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5136,12 +5136,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Holmen 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 3</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5155,17 +5155,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>U11: Sandefjord 1 vs Ringerike 1</t>
+          <t>U11: Holmen 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -5174,17 +5174,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Frisk Asker 1</t>
+          <t>U11: Kongsberg 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -5193,17 +5193,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Jar 3</t>
+          <t>U11: Jar 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -5212,17 +5212,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 1 vs Holmen 1</t>
+          <t>U11: Jar 6 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -5231,17 +5231,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>U11: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U11: Jar 3 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -5250,17 +5250,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>U11: Jar 3 vs Frisk Asker 1</t>
+          <t>U11: Holmen 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -5269,17 +5269,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>U11: Ringerike 1 vs Kongsberg 1</t>
+          <t>U11: Ringerike 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -5288,17 +5288,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>U11: Holmen 1 vs Sandefjord 1</t>
+          <t>U11: Jar 3 vs Holmen 1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -5307,17 +5307,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
+          <t>U11: Kongsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -5326,17 +5326,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Sandefjord 1</t>
+          <t>U11: Ringerike 2 vs Jar 1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -5345,17 +5345,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U11: Holmen 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -5364,17 +5364,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U11: Jar 3 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -5383,12 +5383,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Jar 4</t>
+          <t>U10: Holmen 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Frisk Asker 2</t>
+          <t>U10: Jar 5 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5421,12 +5421,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Ringerike 1</t>
+          <t>U10: Jar 7 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5440,12 +5440,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5459,12 +5459,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 3 vs Holmen 1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Holmen 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Tønsberg 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5516,12 +5516,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jutul 1</t>
+          <t>U10: Holmen 1 vs Jar 1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5535,12 +5535,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Jar 4</t>
+          <t>U10: Frisk Asker 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5554,12 +5554,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
+          <t>U10: Jar 4 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5573,12 +5573,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
+          <t>U10: Jar 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5592,12 +5592,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Frisk Asker 2</t>
+          <t>U10: Jar 5 vs Holmen 1</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5611,12 +5611,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5630,12 +5630,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
+          <t>U10: Frisk Asker 3 vs Jar 1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5649,12 +5649,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5668,12 +5668,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 1</t>
+          <t>U10: Skien 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5687,12 +5687,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 4</t>
+          <t>U10: Jar 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
+          <t>U10: Jar 5 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5725,12 +5725,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Holmen 1</t>
+          <t>U10: Holmen 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5744,12 +5744,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Sandefjord 1</t>
+          <t>U10: Tønsberg 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Jutul 1</t>
+          <t>U10: Jar 4 vs Holmen 1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5782,12 +5782,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 1</t>
+          <t>U10: Frisk Asker 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -5801,12 +5801,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 2</t>
+          <t>U10: Jar 5 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5820,12 +5820,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Kongsberg 1</t>
+          <t>U10: Holmen 1 vs Jar 7</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -5839,12 +5839,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>U10: Ringerike 1 vs Jar 4</t>
+          <t>U10: Skien 1 vs Jar 4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 2 vs Jutul 1</t>
+          <t>U10: Tønsberg 1 vs Holmen 1</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5877,12 +5877,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
+          <t>U10: Jar 7 vs Skien 1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Holmen 1</t>
+          <t>U10: Jar 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -5915,12 +5915,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>U10: Jar 4 vs Frisk Asker 2</t>
+          <t>U10: Jar 4 vs Frisk Asker 3</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -5934,17 +5934,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Kongsberg 1</t>
+          <t>U11: Sandefjord 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -5953,17 +5953,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Sandefjord 1</t>
+          <t>U11: Frisk Asker 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -5972,17 +5972,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Holmen 1</t>
+          <t>U11: Frisk Asker 2 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -5991,12 +5991,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Skien 1</t>
+          <t>U11: Jar 6 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6010,12 +6010,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Tønsberg 1</t>
+          <t>U11: Kongsberg 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jutul 1</t>
+          <t>U11: Sandefjord 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6048,12 +6048,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Jar 5</t>
+          <t>U11: Jar 6 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6067,12 +6067,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Skien 1</t>
+          <t>U11: Jar 2 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6086,12 +6086,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 3</t>
+          <t>U11: Frisk Asker 2 vs Sandefjord 1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6105,12 +6105,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Jutul 1</t>
+          <t>U11: Frisk Asker 1 vs Kongsberg 1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6124,12 +6124,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>U11: Tønsberg 1 vs Ringerike 2</t>
+          <t>U11: Sandefjord 1 vs Frisk Asker 1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6143,12 +6143,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Frisk Asker 3</t>
+          <t>U11: Frisk Asker 2 vs Jar 2</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6162,12 +6162,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>10.04.2027</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Jar 5</t>
+          <t>U11: Kongsberg 1 vs Jar 6</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -6181,17 +6181,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>U11: Frisk Asker 3 vs Jutul 1</t>
+          <t>U10: Skien 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -6200,17 +6200,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>U11: Skien 1 vs Tønsberg 1</t>
+          <t>U10: Jar 6 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -6219,17 +6219,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>U11: Jar 5 vs Frisk Asker 3</t>
+          <t>U10: Jar 2 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -6238,17 +6238,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>U11: Ringerike 2 vs Skien 1</t>
+          <t>U10: Frisk Asker 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -6257,17 +6257,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>U11: Jutul 1 vs Tønsberg 1</t>
+          <t>U10: Ringerike 2 vs Skien 1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -6276,17 +6276,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Tønsberg 1</t>
+          <t>U10: Jutul 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -6295,17 +6295,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Sandefjord 1</t>
+          <t>U10: Frisk Asker 2 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -6314,17 +6314,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
+          <t>U10: Skien 1 vs Jar 3</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -6333,17 +6333,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Kongsberg 1</t>
+          <t>U10: Ringerike 2 vs Jutul 1</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -6352,17 +6352,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Jar 6</t>
+          <t>U10: Jar 5 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -6371,17 +6371,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Frisk Asker 1</t>
+          <t>U10: Jar 3 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -6390,17 +6390,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Ringerike 2</t>
+          <t>U10: Jar 6 vs Skien 1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -6409,17 +6409,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Holmen 1</t>
+          <t>U10: Jutul 1 vs Jar 5</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -6428,17 +6428,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Sandefjord 1</t>
+          <t>U10: Ringerike 2 vs Jar 3</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -6447,17 +6447,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Skien 1</t>
+          <t>U10: Tønsberg 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -6466,17 +6466,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Jutul 1</t>
+          <t>U10: Frisk Asker 2 vs Jar 6</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -6485,17 +6485,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Holmen 1</t>
+          <t>U10: Jar 3 vs Jutul 1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -6504,17 +6504,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jar 6</t>
+          <t>U10: Jar 6 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -6523,17 +6523,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
+          <t>U10: Skien 1 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -6542,17 +6542,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
+          <t>U10: Jutul 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -6561,17 +6561,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Frisk Asker 1</t>
+          <t>U10: Jar 5 vs Skien 1</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -6580,17 +6580,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Kongsberg 1</t>
+          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -6599,17 +6599,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>U10: Skien 1 vs Jutul 1</t>
+          <t>U10: Jar 6 vs Jutul 1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -6618,17 +6618,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>U10: Sandefjord 1 vs Holmen 1</t>
+          <t>U10: Skien 1 vs Jar 2</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -6637,17 +6637,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>U10: Tønsberg 1 vs Ringerike 2</t>
+          <t>U10: Frisk Asker 2 vs Jar 5</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -6656,17 +6656,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>U10: Jutul 1 vs Jar 6</t>
+          <t>U10: Tønsberg 1 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -6675,17 +6675,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
+          <t>U10: Jutul 1 vs Skien 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -6694,17 +6694,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>U10: Ringerike 2 vs Skien 1</t>
+          <t>U10: Jar 2 vs Frisk Asker 2</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -6713,17 +6713,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>U10: Frisk Asker 1 vs Sandefjord 1</t>
+          <t>U10: Jar 3 vs Tønsberg 1</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -6732,1199 +6732,21 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>18.04.2027</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>U10: Jar 6 vs Holmen 1</t>
+          <t>U10: Jar 5 vs Ringerike 2</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>U10: Jutul 1 vs Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Frisk Asker 1</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Jar 6</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>U10: Frisk Asker 1 vs Holmen 1</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>U10: Tønsberg 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>U10: Jar 6 vs Frisk Asker 1</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>U10: Jutul 1 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>U11: Jar 1 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>U11: Frisk Asker 3 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>U11: Ringerike 2 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>U11: Kongsberg 1 vs Jar 1</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>U11: Sandefjord 1 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>U11: Ringerike 2 vs Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>U11: Jar 1 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>U11: Kongsberg 1 vs Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>U11: Jutul 1 vs Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>U11: Ringerike 2 vs Jar 1</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>U11: Frisk Asker 3 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>U11: Jutul 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>U11: Jar 1 vs Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>U11: Ringerike 2 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>10.04.2027</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>U11: Sandefjord 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Varner Arena</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>U10: Frisk Asker 2 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>U10: Skien 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Jar 7</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>U10: Tønsberg 1 vs Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>U10: Jar 7 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>U10: Frisk Asker 2 vs Holmen 1</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>U10: Tønsberg 1 vs Jar 7</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>U10: Jar 7 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>U10: Tønsberg 1 vs Holmen 1</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>U10: Jutul 1 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Jar 7</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>U10: Skien 1 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>U10: Frisk Asker 2 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>U10: Jar 7 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr"/>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>U10: Jutul 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>U10: Ringerike 2 vs Jar 7</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>U10: Frisk Asker 2 vs Skien 1</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>U10: Kongsberg 1 vs Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>U10: Jutul 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>U10: Jar 7 vs Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr"/>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>U10: Skien 1 vs Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>U10: Holmen 1 vs Jutul 1</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>U10: Sandefjord 1 vs Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
